--- a/Use Tax_Disptacher/Data/Config.xlsx
+++ b/Use Tax_Disptacher/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubAnkush\Tax-Use-Automation\Use Tax_Disptacher\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A3B765-17AC-466A-9F5B-5875BD6A2A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25E5377-9A61-4A97-A965-887FC0A96207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -1850,7 +1850,7 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="2" width="65.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97.85546875" customWidth="1"/>
     <col min="3" max="3" width="75.42578125" customWidth="1"/>
     <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
@@ -2192,6 +2192,10 @@
         <v>58</v>
       </c>
       <c r="B42" t="str">
+        <f ca="1">_xlfn.CONCAT("\\twcfileshp01\usershares$\Accounting\Sales Tax\Use Tax\",TEXT(TODAY(),"yyyy")," FY\000FY",TEXT(TODAY(),"yy")," AZ FL PA TX Use Tax Reports\")</f>
+        <v>\\twcfileshp01\usershares$\Accounting\Sales Tax\Use Tax\2026 FY\000FY26 AZ FL PA TX Use Tax Reports\</v>
+      </c>
+      <c r="C42" t="str">
         <f ca="1">_xlfn.CONCAT("\\twcfileshp01\usershares$\Accounting\Sales Tax\Use Tax\",TEXT(TODAY(),"yyyy"),"\000FY",TEXT(TODAY(),"yy")," AZ FL PA TX Use Tax Reports\")</f>
         <v>\\twcfileshp01\usershares$\Accounting\Sales Tax\Use Tax\2026\000FY26 AZ FL PA TX Use Tax Reports\</v>
       </c>
@@ -2202,7 +2206,7 @@
       </c>
       <c r="B43" s="3" t="str">
         <f ca="1">_xlfn.CONCAT("\\twcfileshp01\usershares$\Accounting\Sales Tax\Use Tax\AZ-FL-PA-TX Invoices to verify (Monthly)","\",TEXT(TODAY(),"yyyy"),"\",TEXT(EOMONTH(TODAY(),-1),"mmmm"))</f>
-        <v>\\twcfileshp01\usershares$\Accounting\Sales Tax\Use Tax\AZ-FL-PA-TX Invoices to verify (Monthly)\2026\December</v>
+        <v>\\twcfileshp01\usershares$\Accounting\Sales Tax\Use Tax\AZ-FL-PA-TX Invoices to verify (Monthly)\2026\February</v>
       </c>
       <c r="C43" s="11"/>
     </row>

--- a/Use Tax_Disptacher/Data/Config.xlsx
+++ b/Use Tax_Disptacher/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubAnkush\Tax-Use-Automation\Use Tax_Disptacher\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25E5377-9A61-4A97-A965-887FC0A96207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CCCF67-469A-4B0D-AE1A-E51C4FAD2F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="102">
   <si>
     <t>Name</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>Prod</t>
+  </si>
+  <si>
+    <t>C:\Users\AnkushMyadam\Documents\Uipath Processes\UseTax\</t>
   </si>
 </sst>
 </file>
@@ -766,12 +769,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.5703125" customWidth="1"/>
+    <col min="1" max="1" width="43.5546875" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="81.42578125" customWidth="1"/>
-    <col min="4" max="26" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="81.44140625" customWidth="1"/>
+    <col min="4" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -819,7 +822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="43.2">
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
@@ -831,7 +834,7 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="30">
+    <row r="5" spans="1:26" ht="28.8">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1847,12 +1850,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z983"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="2" width="97.85546875" customWidth="1"/>
-    <col min="3" max="3" width="75.42578125" customWidth="1"/>
-    <col min="4" max="26" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="97.88671875" customWidth="1"/>
+    <col min="3" max="3" width="75.44140625" customWidth="1"/>
+    <col min="4" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -1889,7 +1892,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="30">
+    <row r="2" spans="1:26" ht="28.8">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1900,7 +1903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="43.2">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1984,7 +1987,7 @@
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:3" ht="45">
+    <row r="17" spans="1:3" ht="28.8">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -2082,6 +2085,7 @@
       <c r="B28" s="7" t="s">
         <v>54</v>
       </c>
+      <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1">
       <c r="A29" t="s">
@@ -2090,6 +2094,9 @@
       <c r="B29" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="C29" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1">
       <c r="A30" t="s">
@@ -2206,7 +2213,7 @@
       </c>
       <c r="B43" s="3" t="str">
         <f ca="1">_xlfn.CONCAT("\\twcfileshp01\usershares$\Accounting\Sales Tax\Use Tax\AZ-FL-PA-TX Invoices to verify (Monthly)","\",TEXT(TODAY(),"yyyy"),"\",TEXT(EOMONTH(TODAY(),-1),"mmmm"))</f>
-        <v>\\twcfileshp01\usershares$\Accounting\Sales Tax\Use Tax\AZ-FL-PA-TX Invoices to verify (Monthly)\2026\February</v>
+        <v>\\twcfileshp01\usershares$\Accounting\Sales Tax\Use Tax\AZ-FL-PA-TX Invoices to verify (Monthly)\2026\March</v>
       </c>
       <c r="C43" s="11"/>
     </row>
@@ -3159,12 +3166,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="60.28515625" customWidth="1"/>
-    <col min="4" max="26" width="65.42578125" customWidth="1"/>
+    <col min="1" max="1" width="31.88671875" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" customWidth="1"/>
+    <col min="3" max="3" width="60.33203125" customWidth="1"/>
+    <col min="4" max="26" width="65.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
